--- a/VerveStacks_FRA_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F1B9A72-A7C1-4E25-986F-4A5B58876720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD6194F1-13F1-4244-A643-DFC8B9F5A69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A11BB074-73C4-4474-8591-45E859F27A44}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4C06F40A-A667-4E61-95BB-1B76CAD9C117}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -784,7 +784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1849D256-0C7F-44C0-8D00-B976F45A2FC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352D37DC-3D7C-4D2A-B71C-2D0A6D8CB380}">
   <dimension ref="B3:R44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD6194F1-13F1-4244-A643-DFC8B9F5A69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48369A6-7919-4A98-9A47-F7D022002A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4C06F40A-A667-4E61-95BB-1B76CAD9C117}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3CDF1179-3B30-432A-9350-B4502A8B4B05}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="200">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -401,7 +401,7 @@
     <t>grid link -27.0 km- way/79866837-400;way/99722046-400</t>
   </si>
   <si>
-    <t>~grid_nodes_geo</t>
+    <t>~commodity_geo</t>
   </si>
   <si>
     <t>commodity</t>
@@ -410,10 +410,235 @@
     <t>region</t>
   </si>
   <si>
-    <t>lon</t>
+    <t>lng</t>
   </si>
   <si>
     <t>lat</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_001</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_002</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_004</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_005</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_006</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_007</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_008</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_009</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_010</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_011</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_012</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_013</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_014</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_016</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_017</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_018</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_019</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_020</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_021</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_022</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_023</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_024</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_025</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_026</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_027</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_028</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_029</t>
+  </si>
+  <si>
+    <t>elc_spv_FRA_030</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_001</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_002</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_004</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_005</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_006</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_007</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_008</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_009</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_010</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_011</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_012</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_013</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_014</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_016</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_017</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_001</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_002</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_004</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_005</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_006</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_007</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_008</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_009</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_010</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_011</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_012</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_013</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_014</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_016</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_017</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_018</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_019</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_020</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_021</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_022</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_023</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_024</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_025</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_026</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_027</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_028</t>
   </si>
 </sst>
 </file>
@@ -784,8 +1009,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352D37DC-3D7C-4D2A-B71C-2D0A6D8CB380}">
-  <dimension ref="B3:R44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79C3FBF0-6B8C-40C4-9C2A-06DBCB1F8596}">
+  <dimension ref="B3:R105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -1934,6 +2159,18 @@
       <c r="L31" t="s">
         <v>106</v>
       </c>
+      <c r="O31" t="s">
+        <v>125</v>
+      </c>
+      <c r="P31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q31">
+        <v>2.7758439269287343</v>
+      </c>
+      <c r="R31">
+        <v>49.104541517192352</v>
+      </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
@@ -1963,8 +2200,20 @@
       <c r="L32" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O32" t="s">
+        <v>126</v>
+      </c>
+      <c r="P32" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32">
+        <v>1.6707190992444538</v>
+      </c>
+      <c r="R32">
+        <v>48.256596583270998</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>8</v>
       </c>
@@ -1992,8 +2241,20 @@
       <c r="L33" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O33" t="s">
+        <v>127</v>
+      </c>
+      <c r="P33" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33">
+        <v>3.1264265405264471</v>
+      </c>
+      <c r="R33">
+        <v>50.478653840688978</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -2021,8 +2282,20 @@
       <c r="L34" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O34" t="s">
+        <v>128</v>
+      </c>
+      <c r="P34" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q34">
+        <v>1.5682646596514205</v>
+      </c>
+      <c r="R34">
+        <v>49.782107831111361</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -2050,8 +2323,20 @@
       <c r="L35" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O35" t="s">
+        <v>129</v>
+      </c>
+      <c r="P35" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>-1.4156111766371755</v>
+      </c>
+      <c r="R35">
+        <v>46.900939880628499</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>8</v>
       </c>
@@ -2079,8 +2364,20 @@
       <c r="L36" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O36" t="s">
+        <v>130</v>
+      </c>
+      <c r="P36" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q36">
+        <v>9.5838114964328494E-2</v>
+      </c>
+      <c r="R36">
+        <v>47.486180739811793</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>8</v>
       </c>
@@ -2108,8 +2405,20 @@
       <c r="L37" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O37" t="s">
+        <v>131</v>
+      </c>
+      <c r="P37" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q37">
+        <v>-0.77622421636453831</v>
+      </c>
+      <c r="R37">
+        <v>48.823968315387859</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>8</v>
       </c>
@@ -2137,8 +2446,20 @@
       <c r="L38" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O38" t="s">
+        <v>132</v>
+      </c>
+      <c r="P38" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38">
+        <v>-4.1857770469871918</v>
+      </c>
+      <c r="R38">
+        <v>48.266093519249736</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>8</v>
       </c>
@@ -2166,8 +2487,20 @@
       <c r="L39" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O39" t="s">
+        <v>133</v>
+      </c>
+      <c r="P39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39">
+        <v>-2.5681051361809626</v>
+      </c>
+      <c r="R39">
+        <v>47.979086697649137</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>8</v>
       </c>
@@ -2195,8 +2528,20 @@
       <c r="L40" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O40" t="s">
+        <v>134</v>
+      </c>
+      <c r="P40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q40">
+        <v>7.1082382279880107</v>
+      </c>
+      <c r="R40">
+        <v>48.830161509925112</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>8</v>
       </c>
@@ -2224,8 +2569,20 @@
       <c r="L41" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O41" t="s">
+        <v>135</v>
+      </c>
+      <c r="P41" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41">
+        <v>6.4171067531158323</v>
+      </c>
+      <c r="R41">
+        <v>47.708301406981562</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>8</v>
       </c>
@@ -2253,8 +2610,20 @@
       <c r="L42" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O42" t="s">
+        <v>136</v>
+      </c>
+      <c r="P42" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>4.7432904268725489</v>
+      </c>
+      <c r="R42">
+        <v>49.664920028384877</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>8</v>
       </c>
@@ -2282,8 +2651,20 @@
       <c r="L43" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O43" t="s">
+        <v>137</v>
+      </c>
+      <c r="P43" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43">
+        <v>3.9577097528045457</v>
+      </c>
+      <c r="R43">
+        <v>47.796105752097226</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>8</v>
       </c>
@@ -2310,6 +2691,872 @@
       </c>
       <c r="L44" t="s">
         <v>119</v>
+      </c>
+      <c r="O44" t="s">
+        <v>138</v>
+      </c>
+      <c r="P44" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44">
+        <v>4.5874102564850929</v>
+      </c>
+      <c r="R44">
+        <v>48.680798254605719</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O45" t="s">
+        <v>139</v>
+      </c>
+      <c r="P45" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45">
+        <v>4.4520789172497333</v>
+      </c>
+      <c r="R45">
+        <v>43.952599727682561</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O46" t="s">
+        <v>140</v>
+      </c>
+      <c r="P46" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46">
+        <v>3.0323219079836812</v>
+      </c>
+      <c r="R46">
+        <v>43.16586702605882</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O47" t="s">
+        <v>141</v>
+      </c>
+      <c r="P47" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47">
+        <v>9.0821325477055037</v>
+      </c>
+      <c r="R47">
+        <v>41.959595077451752</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O48" t="s">
+        <v>142</v>
+      </c>
+      <c r="P48" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48">
+        <v>6.5473156779806585</v>
+      </c>
+      <c r="R48">
+        <v>44.096324886431738</v>
+      </c>
+    </row>
+    <row r="49" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O49" t="s">
+        <v>143</v>
+      </c>
+      <c r="P49" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49">
+        <v>5.8196466748485802</v>
+      </c>
+      <c r="R49">
+        <v>46.653515304349867</v>
+      </c>
+    </row>
+    <row r="50" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O50" t="s">
+        <v>144</v>
+      </c>
+      <c r="P50" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q50">
+        <v>5.7986597490618434</v>
+      </c>
+      <c r="R50">
+        <v>45.478338310193443</v>
+      </c>
+    </row>
+    <row r="51" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O51" t="s">
+        <v>145</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51">
+        <v>2.001767181157065</v>
+      </c>
+      <c r="R51">
+        <v>44.290533984237271</v>
+      </c>
+    </row>
+    <row r="52" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O52" t="s">
+        <v>146</v>
+      </c>
+      <c r="P52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52">
+        <v>3.1519783648903288</v>
+      </c>
+      <c r="R52">
+        <v>46.722452442616479</v>
+      </c>
+    </row>
+    <row r="53" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O53" t="s">
+        <v>147</v>
+      </c>
+      <c r="P53" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q53">
+        <v>4.6625883323343196</v>
+      </c>
+      <c r="R53">
+        <v>46.447606877182309</v>
+      </c>
+    </row>
+    <row r="54" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O54" t="s">
+        <v>148</v>
+      </c>
+      <c r="P54" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54">
+        <v>3.451685305655162</v>
+      </c>
+      <c r="R54">
+        <v>45.463073942632548</v>
+      </c>
+    </row>
+    <row r="55" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O55" t="s">
+        <v>149</v>
+      </c>
+      <c r="P55" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q55">
+        <v>-1.1264311785239347</v>
+      </c>
+      <c r="R55">
+        <v>43.723820011228149</v>
+      </c>
+    </row>
+    <row r="56" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O56" t="s">
+        <v>150</v>
+      </c>
+      <c r="P56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q56">
+        <v>0.66680597675455422</v>
+      </c>
+      <c r="R56">
+        <v>43.409636926634803</v>
+      </c>
+    </row>
+    <row r="57" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O57" t="s">
+        <v>151</v>
+      </c>
+      <c r="P57" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57">
+        <v>1.7332229008287714</v>
+      </c>
+      <c r="R57">
+        <v>45.551388524314461</v>
+      </c>
+    </row>
+    <row r="58" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O58" t="s">
+        <v>152</v>
+      </c>
+      <c r="P58" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58">
+        <v>0.79547462866156815</v>
+      </c>
+      <c r="R58">
+        <v>46.191406136928052</v>
+      </c>
+    </row>
+    <row r="59" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O59" t="s">
+        <v>153</v>
+      </c>
+      <c r="P59" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59">
+        <v>0.12147997257367089</v>
+      </c>
+      <c r="R59">
+        <v>44.350126294808717</v>
+      </c>
+    </row>
+    <row r="60" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O60" t="s">
+        <v>154</v>
+      </c>
+      <c r="P60" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60">
+        <v>-0.72951060260121037</v>
+      </c>
+      <c r="R60">
+        <v>45.393581429475283</v>
+      </c>
+    </row>
+    <row r="61" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O61" t="s">
+        <v>155</v>
+      </c>
+      <c r="P61" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q61">
+        <v>4.0891653056977164</v>
+      </c>
+      <c r="R61">
+        <v>42.905888415052182</v>
+      </c>
+    </row>
+    <row r="62" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O62" t="s">
+        <v>156</v>
+      </c>
+      <c r="P62" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62">
+        <v>9.6941685291356539</v>
+      </c>
+      <c r="R62">
+        <v>43.477722315914733</v>
+      </c>
+    </row>
+    <row r="63" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O63" t="s">
+        <v>157</v>
+      </c>
+      <c r="P63" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q63">
+        <v>9.6690899760889444</v>
+      </c>
+      <c r="R63">
+        <v>43.028062134052448</v>
+      </c>
+    </row>
+    <row r="64" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O64" t="s">
+        <v>158</v>
+      </c>
+      <c r="P64" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q64">
+        <v>7.96232065735144</v>
+      </c>
+      <c r="R64">
+        <v>43.477722315914725</v>
+      </c>
+    </row>
+    <row r="65" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O65" t="s">
+        <v>159</v>
+      </c>
+      <c r="P65" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q65">
+        <v>9.6980824775382839</v>
+      </c>
+      <c r="R65">
+        <v>41.679081588465642</v>
+      </c>
+    </row>
+    <row r="66" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O66" t="s">
+        <v>160</v>
+      </c>
+      <c r="P66" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>8.5616828125837916</v>
+      </c>
+      <c r="R66">
+        <v>42.578401952190191</v>
+      </c>
+    </row>
+    <row r="67" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O67" t="s">
+        <v>161</v>
+      </c>
+      <c r="P67" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q67">
+        <v>5.9418167504611654</v>
+      </c>
+      <c r="R67">
+        <v>43.028062134052462</v>
+      </c>
+    </row>
+    <row r="68" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O68" t="s">
+        <v>162</v>
+      </c>
+      <c r="P68" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q68">
+        <v>5.5648720364220337</v>
+      </c>
+      <c r="R68">
+        <v>43.477722315914725</v>
+      </c>
+    </row>
+    <row r="69" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O69" t="s">
+        <v>163</v>
+      </c>
+      <c r="P69" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q69">
+        <v>-1.8500303581743529</v>
+      </c>
+      <c r="R69">
+        <v>44.275854961528658</v>
+      </c>
+    </row>
+    <row r="70" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O70" t="s">
+        <v>164</v>
+      </c>
+      <c r="P70" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q70">
+        <v>-1.6274738263661856</v>
+      </c>
+      <c r="R70">
+        <v>43.477722315914725</v>
+      </c>
+    </row>
+    <row r="71" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O71" t="s">
+        <v>165</v>
+      </c>
+      <c r="P71" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q71">
+        <v>-2.655456225601712</v>
+      </c>
+      <c r="R71">
+        <v>45.67925560198433</v>
+      </c>
+    </row>
+    <row r="72" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O72" t="s">
+        <v>166</v>
+      </c>
+      <c r="P72" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72">
+        <v>-4.0249512555042291</v>
+      </c>
+      <c r="R72">
+        <v>46.864713781272151</v>
+      </c>
+    </row>
+    <row r="73" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O73" t="s">
+        <v>167</v>
+      </c>
+      <c r="P73" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q73">
+        <v>-3.1633638781170359</v>
+      </c>
+      <c r="R73">
+        <v>49.246496197452707</v>
+      </c>
+    </row>
+    <row r="74" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O74" t="s">
+        <v>168</v>
+      </c>
+      <c r="P74" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q74">
+        <v>-1.5765559657675094</v>
+      </c>
+      <c r="R74">
+        <v>50.082385512798339</v>
+      </c>
+    </row>
+    <row r="75" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O75" t="s">
+        <v>169</v>
+      </c>
+      <c r="P75" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q75">
+        <v>-5.3135945051867868</v>
+      </c>
+      <c r="R75">
+        <v>48.919223059344517</v>
+      </c>
+    </row>
+    <row r="76" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O76" t="s">
+        <v>170</v>
+      </c>
+      <c r="P76" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q76">
+        <v>-5.4230546467189598</v>
+      </c>
+      <c r="R76">
+        <v>47.599320798730083</v>
+      </c>
+    </row>
+    <row r="77" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O77" t="s">
+        <v>171</v>
+      </c>
+      <c r="P77" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q77">
+        <v>-7.0141753205051653</v>
+      </c>
+      <c r="R77">
+        <v>48.278603811293763</v>
+      </c>
+    </row>
+    <row r="78" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O78" t="s">
+        <v>172</v>
+      </c>
+      <c r="P78" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q78">
+        <v>9.1030602941814678</v>
+      </c>
+      <c r="R78">
+        <v>42.614218545101856</v>
+      </c>
+    </row>
+    <row r="79" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O79" t="s">
+        <v>173</v>
+      </c>
+      <c r="P79" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q79">
+        <v>6.3166894571172252</v>
+      </c>
+      <c r="R79">
+        <v>43.513538908826384</v>
+      </c>
+    </row>
+    <row r="80" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O80" t="s">
+        <v>174</v>
+      </c>
+      <c r="P80" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q80">
+        <v>7.9039193734542552</v>
+      </c>
+      <c r="R80">
+        <v>43.963199090688668</v>
+      </c>
+    </row>
+    <row r="81" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O81" t="s">
+        <v>175</v>
+      </c>
+      <c r="P81" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81">
+        <v>5.5056375319998336</v>
+      </c>
+      <c r="R81">
+        <v>44.070821597772323</v>
+      </c>
+    </row>
+    <row r="82" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O82" t="s">
+        <v>176</v>
+      </c>
+      <c r="P82" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q82">
+        <v>6.1052079923634377</v>
+      </c>
+      <c r="R82">
+        <v>43.963199090688668</v>
+      </c>
+    </row>
+    <row r="83" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O83" t="s">
+        <v>177</v>
+      </c>
+      <c r="P83" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83">
+        <v>4.6164848912923393</v>
+      </c>
+      <c r="R83">
+        <v>44.509668527821503</v>
+      </c>
+    </row>
+    <row r="84" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O84" t="s">
+        <v>178</v>
+      </c>
+      <c r="P84" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q84">
+        <v>3.1172273848784822</v>
+      </c>
+      <c r="R84">
+        <v>43.538653048977203</v>
+      </c>
+    </row>
+    <row r="85" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O85" t="s">
+        <v>179</v>
+      </c>
+      <c r="P85" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q85">
+        <v>5.1285445766018318</v>
+      </c>
+      <c r="R85">
+        <v>45.833541585538022</v>
+      </c>
+    </row>
+    <row r="86" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O86" t="s">
+        <v>180</v>
+      </c>
+      <c r="P86" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q86">
+        <v>3.3807615922775867</v>
+      </c>
+      <c r="R86">
+        <v>45.312152088373935</v>
+      </c>
+    </row>
+    <row r="87" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O87" t="s">
+        <v>181</v>
+      </c>
+      <c r="P87" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q87">
+        <v>-0.73950683310636656</v>
+      </c>
+      <c r="R87">
+        <v>44.293722236799809</v>
+      </c>
+    </row>
+    <row r="88" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O88" t="s">
+        <v>182</v>
+      </c>
+      <c r="P88" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q88">
+        <v>2.7995560800912801E-2</v>
+      </c>
+      <c r="R88">
+        <v>43.660962299586188</v>
+      </c>
+    </row>
+    <row r="89" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O89" t="s">
+        <v>183</v>
+      </c>
+      <c r="P89" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89">
+        <v>-1.427268245024125</v>
+      </c>
+      <c r="R89">
+        <v>43.063878726964127</v>
+      </c>
+    </row>
+    <row r="90" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O90" t="s">
+        <v>184</v>
+      </c>
+      <c r="P90" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q90">
+        <v>2.0176719174154121</v>
+      </c>
+      <c r="R90">
+        <v>44.006274888000739</v>
+      </c>
+    </row>
+    <row r="91" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O91" t="s">
+        <v>185</v>
+      </c>
+      <c r="P91" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91">
+        <v>0.53896208216297503</v>
+      </c>
+      <c r="R91">
+        <v>42.871465728448371</v>
+      </c>
+    </row>
+    <row r="92" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O92" t="s">
+        <v>186</v>
+      </c>
+      <c r="P92" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q92">
+        <v>4.6421685129783876</v>
+      </c>
+      <c r="R92">
+        <v>49.73275586302136</v>
+      </c>
+    </row>
+    <row r="93" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O93" t="s">
+        <v>187</v>
+      </c>
+      <c r="P93" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q93">
+        <v>1.972373369098342</v>
+      </c>
+      <c r="R93">
+        <v>49.654475583771223</v>
+      </c>
+    </row>
+    <row r="94" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O94" t="s">
+        <v>188</v>
+      </c>
+      <c r="P94" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94">
+        <v>-1.6892079923634395</v>
+      </c>
+      <c r="R94">
+        <v>49.359121273035917</v>
+      </c>
+    </row>
+    <row r="95" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O95" t="s">
+        <v>189</v>
+      </c>
+      <c r="P95" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q95">
+        <v>-1.1840541884497655</v>
+      </c>
+      <c r="R95">
+        <v>47.953859066083943</v>
+      </c>
+    </row>
+    <row r="96" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O96" t="s">
+        <v>190</v>
+      </c>
+      <c r="P96" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96">
+        <v>7.8726515820334031</v>
+      </c>
+      <c r="R96">
+        <v>48.674557618005572</v>
+      </c>
+    </row>
+    <row r="97" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O97" t="s">
+        <v>191</v>
+      </c>
+      <c r="P97" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q97">
+        <v>6.0821754877937666</v>
+      </c>
+      <c r="R97">
+        <v>48.850262013243011</v>
+      </c>
+    </row>
+    <row r="98" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O98" t="s">
+        <v>192</v>
+      </c>
+      <c r="P98" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q98">
+        <v>7.4857754468941922</v>
+      </c>
+      <c r="R98">
+        <v>47.712086968169707</v>
+      </c>
+    </row>
+    <row r="99" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O99" t="s">
+        <v>193</v>
+      </c>
+      <c r="P99" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q99">
+        <v>6.4291285856667324</v>
+      </c>
+      <c r="R99">
+        <v>47.327078939818641</v>
+      </c>
+    </row>
+    <row r="100" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O100" t="s">
+        <v>194</v>
+      </c>
+      <c r="P100" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100">
+        <v>5.3435265776984711</v>
+      </c>
+      <c r="R100">
+        <v>47.346434089868303</v>
+      </c>
+    </row>
+    <row r="101" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O101" t="s">
+        <v>195</v>
+      </c>
+      <c r="P101" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101">
+        <v>3.0973028371004379</v>
+      </c>
+      <c r="R101">
+        <v>46.589351878095599</v>
+      </c>
+    </row>
+    <row r="102" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O102" t="s">
+        <v>196</v>
+      </c>
+      <c r="P102" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102">
+        <v>2.9095154825731595</v>
+      </c>
+      <c r="R102">
+        <v>47.999473215219247</v>
+      </c>
+    </row>
+    <row r="103" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O103" t="s">
+        <v>197</v>
+      </c>
+      <c r="P103" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q103">
+        <v>0.18316130996753971</v>
+      </c>
+      <c r="R103">
+        <v>46.534780180925409</v>
+      </c>
+    </row>
+    <row r="104" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O104" t="s">
+        <v>198</v>
+      </c>
+      <c r="P104" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q104">
+        <v>0.78058095640076319</v>
+      </c>
+      <c r="R104">
+        <v>44.621359237914632</v>
+      </c>
+    </row>
+    <row r="105" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O105" t="s">
+        <v>199</v>
+      </c>
+      <c r="P105" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q105">
+        <v>0.7212251633585669</v>
+      </c>
+      <c r="R105">
+        <v>45.519480102186293</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48369A6-7919-4A98-9A47-F7D022002A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E53062A3-7635-483E-BDDE-99396F14BF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3CDF1179-3B30-432A-9350-B4502A8B4B05}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4A045260-9ED2-4BEB-B352-858824252DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1009,7 +1009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79C3FBF0-6B8C-40C4-9C2A-06DBCB1F8596}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2AA0111-3363-44C6-BD38-ECC31B73A1E3}">
   <dimension ref="B3:R105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
